--- a/DIFF_PREVIOUS/Mod_Korean/Lang/KR/Game/Block.xlsx
+++ b/DIFF_PREVIOUS/Mod_Korean/Lang/KR/Game/Block.xlsx
@@ -23,7 +23,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1102" uniqueCount="580">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1112" uniqueCount="583">
   <si>
     <t xml:space="preserve">id</t>
   </si>
@@ -1039,7 +1039,7 @@
     <t xml:space="preserve">특수 블록 (투명)</t>
   </si>
   <si>
-    <t xml:space="preserve">Editor Block(Invisiblel)</t>
+    <t xml:space="preserve">Special Block (Invisible)</t>
   </si>
   <si>
     <t xml:space="preserve">特殊ブロック(透明)</t>
@@ -1204,7 +1204,7 @@
     <t xml:space="preserve">특수 블록 (실내)</t>
   </si>
   <si>
-    <t xml:space="preserve">Editor Block(Interior)</t>
+    <t xml:space="preserve">Special Block (Interior)</t>
   </si>
   <si>
     <t xml:space="preserve">特殊ブロック(室内)</t>
@@ -1216,7 +1216,7 @@
     <t xml:space="preserve">특수 블록 (야외)</t>
   </si>
   <si>
-    <t xml:space="preserve">Editor Block(Exterior)</t>
+    <t xml:space="preserve">Special Block (Exterior)</t>
   </si>
   <si>
     <t xml:space="preserve">特殊ブロック(野外)</t>
@@ -1763,6 +1763,15 @@
   </si>
   <si>
     <t xml:space="preserve">217</t>
+  </si>
+  <si>
+    <t xml:space="preserve">218</t>
+  </si>
+  <si>
+    <t xml:space="preserve">EA 23.352</t>
+  </si>
+  <si>
+    <t xml:space="preserve">219</t>
   </si>
 </sst>
 </file>
@@ -1991,7 +2000,7 @@
   <sheetPr filterMode="false">
     <pageSetUpPr fitToPage="false"/>
   </sheetPr>
-  <dimension ref="A1:H220"/>
+  <dimension ref="A1:H222"/>
   <sheetFormatPr defaultColWidth="8.7578125" defaultRowHeight="15" customHeight="false" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="8" min="1" style="0" width="16.15"/>
@@ -5739,6 +5748,40 @@
       </c>
       <c r="E220" s="0" t="s">
         <v>216</v>
+      </c>
+    </row>
+    <row r="221" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A221" s="0" t="s">
+        <v>580</v>
+      </c>
+      <c r="B221" s="0" t="s">
+        <v>581</v>
+      </c>
+      <c r="C221" s="0" t="s">
+        <v>44</v>
+      </c>
+      <c r="D221" s="0" t="s">
+        <v>45</v>
+      </c>
+      <c r="E221" s="0" t="s">
+        <v>46</v>
+      </c>
+    </row>
+    <row r="222" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A222" s="0" t="s">
+        <v>582</v>
+      </c>
+      <c r="B222" s="0" t="s">
+        <v>581</v>
+      </c>
+      <c r="C222" s="0" t="s">
+        <v>292</v>
+      </c>
+      <c r="D222" s="0" t="s">
+        <v>293</v>
+      </c>
+      <c r="E222" s="0" t="s">
+        <v>294</v>
       </c>
     </row>
   </sheetData>
